--- a/astro-site/public/dl/coffee-shop-checklist-templates/07-blank-coffee-shop-checklist-template.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/07-blank-coffee-shop-checklist-template.xlsx
@@ -1981,7 +1981,7 @@
       <c r="C6" s="30" t="n"/>
       <c r="D6" s="31" t="inlineStr">
         <is>
-          <t>Head chef</t>
+          <t>Kitchen lead</t>
         </is>
       </c>
       <c r="E6" s="31" t="inlineStr">
@@ -2000,7 +2000,7 @@
       <c r="C7" s="30" t="n"/>
       <c r="D7" s="31" t="inlineStr">
         <is>
-          <t>Head chef</t>
+          <t>Kitchen lead</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       <c r="C8" s="30" t="n"/>
       <c r="D8" s="31" t="inlineStr">
         <is>
-          <t>Head chef</t>
+          <t>Kitchen lead</t>
         </is>
       </c>
       <c r="E8" s="31" t="inlineStr"/>
@@ -2030,7 +2030,7 @@
       <c r="C9" s="30" t="n"/>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>Head chef</t>
+          <t>Kitchen lead</t>
         </is>
       </c>
       <c r="E9" s="31" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       <c r="C10" s="30" t="n"/>
       <c r="D10" s="31" t="inlineStr">
         <is>
-          <t>Head chef</t>
+          <t>Kitchen lead</t>
         </is>
       </c>
       <c r="E10" s="31" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       <c r="C13" s="30" t="n"/>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>FOH manager</t>
+          <t>Shift lead</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
@@ -2101,7 +2101,7 @@
       <c r="C14" s="30" t="n"/>
       <c r="D14" s="31" t="inlineStr">
         <is>
-          <t>FOH manager</t>
+          <t>Shift lead</t>
         </is>
       </c>
       <c r="E14" s="31" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
       <c r="C15" s="30" t="n"/>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>FOH manager</t>
+          <t>Shift lead</t>
         </is>
       </c>
       <c r="E15" s="31" t="inlineStr"/>
@@ -2131,7 +2131,7 @@
       <c r="C16" s="30" t="n"/>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>FOH manager</t>
+          <t>Shift lead</t>
         </is>
       </c>
       <c r="E16" s="31" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       <c r="C17" s="30" t="n"/>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>FOH manager</t>
+          <t>Shift lead</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
       <c r="C20" s="30" t="n"/>
       <c r="D20" s="31" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="C21" s="30" t="n"/>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr"/>
@@ -2217,7 +2217,7 @@
       <c r="C22" s="30" t="n"/>
       <c r="D22" s="31" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr"/>
@@ -2232,7 +2232,7 @@
       <c r="C23" s="30" t="n"/>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
       <c r="C24" s="30" t="n"/>
       <c r="D24" s="31" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr"/>
